--- a/liste prix ventes articles part4.xlsx
+++ b/liste prix ventes articles part4.xlsx
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="720">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="726">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>SAVON LISSA WHITE CREME GOM MIELA LA BAVE DESCARGOT</t>
+          <t>SAVON LISSA WHITE GOM MIEL &amp; BAVE ESCARGOT 200G</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>SAVON LANALUX PECHE 120G</t>
+          <t>SAVON LANALUX ASS 120G</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -15085,7 +15085,7 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="979">
@@ -15486,11 +15486,11 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>SHAMPOING BAMBINO 900ML ASS</t>
+          <t>GEL LAVANT  BAMBINO 900ML ASS</t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1006">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1009">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>VIN COLORES SANTOS 2021 CARB SYRAH 750ML</t>
+          <t>VIN COLORES SANTOS CARMENERE SYRAH 750ML</t>
         </is>
       </c>
       <c r="C1385" t="n">
